--- a/Proyecto 1 - Etapa 2/datos_noticias.xlsx
+++ b/Proyecto 1 - Etapa 2/datos_noticias.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/a_chaparrod_uniandes_edu_co/Documents/Escritorio/universidad/Semestre 9/Inteligencia de negocios/Proyecto01-BI/Proyecto 1 - Etapa 2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_CC2ABEC597D9AE9F01796BA1486E729560B43C13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E723C12-1399-4F8A-B169-563446AF1150}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>ID</t>
   </si>
@@ -26,15 +32,6 @@
   </si>
   <si>
     <t>Fecha</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
   </si>
   <si>
     <t>La ley de igualdad de trato se debatirá en el Congreso pese a las críticas de Unidas Podemos de 'obstaculizar' la ley 'trans'</t>
@@ -61,8 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,13 +122,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -169,7 +174,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -203,6 +208,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -237,9 +243,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -412,11 +419,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,46 +437,46 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
